--- a/workshop_ratings_output.xlsx
+++ b/workshop_ratings_output.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,13 +33,8 @@
     <font>
       <sz val="10"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="007B3F00"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,16 +49,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD966"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,18 +78,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -475,7 +454,7 @@
   <dimension ref="A1:AH2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -502,7 +481,7 @@
     <col width="7" customWidth="1" min="25" max="25"/>
     <col width="7" customWidth="1" min="26" max="26"/>
     <col width="7" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="7" customWidth="1" min="28" max="28"/>
     <col width="7" customWidth="1" min="29" max="29"/>
     <col width="7" customWidth="1" min="30" max="30"/>
     <col width="7" customWidth="1" min="31" max="31"/>
@@ -686,12 +665,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>form1.jpeg</t>
+          <t>sampleform.jpeg</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02 19:47:07</t>
+          <t>2026-09-29 12:32:00</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -769,10 +748,8 @@
       <c r="AA2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AB2" s="3" t="inlineStr">
-        <is>
-          <t>ILLEGIBLE</t>
-        </is>
+      <c r="AB2" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="AC2" s="2" t="n">
         <v>5</v>
@@ -786,14 +763,10 @@
       <c r="AF2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AG2" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH2" s="2" t="inlineStr">
-        <is>
-          <t>Flag: Q26</t>
-        </is>
-      </c>
+      <c r="AG2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
